--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/8481-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/8481-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DB5D2D9D-8EF2-4159-B6E5-C56E518CB20A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{77A0C7F3-99CD-4CA8-A9EE-EC834725AFB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{F7F273E6-9DFA-4F75-974C-EEC388D04C3C}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{B01C96C4-ED34-4655-9F69-E8C5BF0B9CCF}"/>
   </bookViews>
   <sheets>
     <sheet name="8481-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1436,26 +1436,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EE69C1A2-FCB3-4C20-BA90-38E1CCB1A6BE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D59A2C0B-1037-4730-B7B1-15ACE876BB67}">
   <dimension ref="A1:X15"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="11.375" customWidth="1"/>
-    <col min="3" max="3" width="10.25" customWidth="1"/>
-    <col min="4" max="5" width="6.25" customWidth="1"/>
-    <col min="6" max="6" width="6.625" customWidth="1"/>
-    <col min="7" max="9" width="6.25" customWidth="1"/>
-    <col min="10" max="10" width="6.625" customWidth="1"/>
-    <col min="11" max="13" width="6.25" customWidth="1"/>
-    <col min="14" max="14" width="6.625" customWidth="1"/>
-    <col min="15" max="18" width="6.25" customWidth="1"/>
-    <col min="19" max="19" width="6.625" customWidth="1"/>
-    <col min="20" max="22" width="6.25" customWidth="1"/>
-    <col min="23" max="23" width="6.625" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
@@ -1489,7 +1488,7 @@
       <c r="W1" s="26"/>
       <c r="X1" s="18"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
@@ -1525,7 +1524,7 @@
       <c r="W2" s="28"/>
       <c r="X2" s="29"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="19" t="s">
         <v>2</v>
       </c>
@@ -1577,7 +1576,7 @@
       </c>
       <c r="X3" s="32"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="21"/>
       <c r="B4" s="22"/>
       <c r="C4" s="7"/>
@@ -1645,7 +1644,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="33">
         <v>2024</v>
       </c>
@@ -1717,7 +1716,7 @@
         <v>6.34</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="35">
         <v>2023</v>
       </c>
@@ -1789,7 +1788,7 @@
         <v>4.26</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="33">
         <v>2022</v>
       </c>
@@ -1861,7 +1860,7 @@
         <v>7.58</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="35">
         <v>2021</v>
       </c>
@@ -1933,7 +1932,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="33">
         <v>2020</v>
       </c>
@@ -2005,7 +2004,7 @@
         <v>10.1</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2019</v>
       </c>
@@ -2077,7 +2076,7 @@
         <v>6.7</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="33">
         <v>2018</v>
       </c>
@@ -2149,7 +2148,7 @@
         <v>6.21</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="35">
         <v>2017</v>
       </c>
@@ -2221,7 +2220,7 @@
         <v>7.28</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="33">
         <v>2016</v>
       </c>
@@ -2293,7 +2292,7 @@
         <v>4.22</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="35">
         <v>2015</v>
       </c>
@@ -2365,7 +2364,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="33" t="s">
         <v>38</v>
       </c>
